--- a/data/seed/portfolio/L-2025-2904/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-2904/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,35 +542,35 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>2365000</v>
+        <v>4013000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №109/26 от 01.07.2026</t>
+          <t>Yetkazilgan tovar uchunto'lov h/f №8301</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33765000</v>
+        <v>35413000</v>
       </c>
     </row>
     <row r="9">
@@ -582,35 +582,35 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>7158000</v>
+        <v>3645000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8783 02.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №58/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>40923000</v>
+        <v>39058000</v>
       </c>
     </row>
     <row r="10">
@@ -622,21 +622,21 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>3361000</v>
+        <v>3273000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,11 +646,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №96/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44284000</v>
+        <v>42331000</v>
       </c>
     </row>
     <row r="11">
@@ -662,35 +662,35 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>1273000</v>
+        <v>2475000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9417 02.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>45557000</v>
+        <v>44806000</v>
       </c>
     </row>
     <row r="12">
@@ -700,103 +700,103 @@
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>11989000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>975000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №203/26</t>
+          <t>Оплата по счет-фактуре №6712 за поставленный товар</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33568000</v>
+        <v>45781000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>45452000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>1480000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №170/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3803 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-11884000</v>
+        <v>47261000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>6626000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>5562000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Bunyodkor Plastik MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>346876819</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000012955226001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -806,11 +806,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktur №6025 06.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №107/26</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-5258000</v>
+        <v>41699000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>6065000</v>
+        <v>2621000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Termiz Metall MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7059</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7160</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>807000</v>
+        <v>44320000</v>
       </c>
     </row>
     <row r="16">
@@ -862,35 +862,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>5217000</v>
+        <v>960000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7315 06.07.2026, QQS bilan</t>
+          <t>Shartnoma №184/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6024000</v>
+        <v>45280000</v>
       </c>
     </row>
     <row r="17">
@@ -902,35 +902,35 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>1550000</v>
+        <v>755000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shartnoma №38/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7574000</v>
+        <v>46035000</v>
       </c>
     </row>
     <row r="18">
@@ -941,97 +941,97 @@
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>11537000</v>
+        <v>3473000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №217/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-3963000</v>
+        <v>42562000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>10186000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>11537000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>309305032</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №29/26, НДС 12%</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №2598</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6223000</v>
+        <v>31025000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>2009000</v>
+        <v>9537000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1041,77 +1041,77 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1309 08.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №14/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8232000</v>
+        <v>40562000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1553000</v>
+        <v>8249000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish Materiallari AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>295868307</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000737520516001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Оплата за товары согласно счет-фактуре №5049</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6679000</v>
+        <v>32313000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>4009000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>1553000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>390795382</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000362230014001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,192 +1121,197 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №226/26, QQS 12%</t>
+          <t>Арендная плата за июль 2026 г. по договору №13/22</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>10688000</v>
+        <v>30760000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>10500000</v>
+        <v>9448000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16307000289377189417</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>ОПЛАТАЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №4313</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>188000</v>
+        <v>21312000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>3112000</v>
+        <v>16366000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>339798935</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000299363680001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Shartnoma №156/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3300000</v>
+        <v>37678000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>9308000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>7996000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №295/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №850 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-6008000</v>
+        <v>45674000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>6262000</v>
+        <v>922000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5349 15.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №3327 за поставленный товар</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>254000</v>
+        <v>46596000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>2029000</v>
+        <v>1844000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,237 +1321,232 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №162/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №105 за поставленный товар</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2283000</v>
+        <v>48440000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1573000</v>
+        <v>4033000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Оплата за сырье по дог. №211/26 от 10.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>710000</v>
+        <v>44407000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1573000</v>
+        <v>10500000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000289377189417</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-863000</v>
+        <v>33907000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>48690000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>789000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Shodlik Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>379893522</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000936368057001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №29/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №4/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-49553000</v>
+        <v>34696000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>113135000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>3987000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №103/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8795</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>63582000</v>
+        <v>30709000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2977000</v>
+        <v>5235000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Farg'ona Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>241082476</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000569424555001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №270/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №865</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>60605000</v>
+        <v>25474000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>5290000</v>
+        <v>2462000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,37 +1556,37 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7930 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №6858 за поставленный товар</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>65895000</v>
+        <v>27936000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>2262000</v>
+        <v>1606000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1596,77 +1596,77 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4034 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №7160 за поставленный товар</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>68157000</v>
+        <v>29542000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>2218000</v>
+        <v>721000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №205/26, QQS 12%</t>
+          <t>Shartnoma №30/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>70375000</v>
+        <v>30263000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2707000</v>
+        <v>7066000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1676,357 +1676,357 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №238/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №75/26, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>67668000</v>
+        <v>23197000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>39387000</v>
+        <v>1573000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2248</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>28281000</v>
+        <v>21624000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>4630000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>1573000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №3/26, QQS 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32911000</v>
+        <v>20051000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2558000</v>
+        <v>5387000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за транспортные услуги по договору №2/26</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>30353000</v>
+        <v>14664000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>10479000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>7053000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3737</t>
+          <t>Оплата за сырье по дог. №255/26 от 15.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40832000</v>
+        <v>7611000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>3592000</v>
+        <v>6868000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Termiz Metall MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7770 23.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №307 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>44424000</v>
+        <v>14479000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>17199000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>1326000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №203/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2787 за поставленный товар</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27225000</v>
+        <v>15805000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>971000</v>
+        <v>16008000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000783144546001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №8048</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26254000</v>
+        <v>-203000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>5526000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>56577000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №147/26</t>
+          <t>Предоплата за товар по дог. №158/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20728000</v>
+        <v>56374000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46231</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>7580000</v>
+        <v>4106000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2036,232 +2036,237 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №549 28.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №57/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>28308000</v>
+        <v>60480000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>2777000</v>
+        <v>1507000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7493</t>
+          <t>Оплата за товар по счет-фактуре №6052 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>31085000</v>
+        <v>61987000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46234</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>957000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Ishonch Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за товар по с/ф №4619 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>30785000</v>
+        <v>62944000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>9216000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>9582000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5444</t>
+          <t>Оплата за сырье по договору №292/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>40001000</v>
+        <v>53362000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>5440000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>13106000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8060 03.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по дог. №33/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>45441000</v>
+        <v>40256000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>4007000</v>
+        <v>984000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kamalak Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>356185384</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000620555350001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №291/26 от 03.08.2026</t>
+          <t>Оплата по с/ф №1505 за поставленный товар</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>49448000</v>
+        <v>41240000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>3905000</v>
+        <v>683000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2271,37 +2276,37 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №256 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5331 за поставленный товар</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>53353000</v>
+        <v>41923000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>3202000</v>
+        <v>6588000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2311,77 +2316,77 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2956 за поставленный товар</t>
+          <t>Предоплата за товар по договору №39/26 от 22.07.2026</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>56555000</v>
+        <v>48511000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>2295000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>2577000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8597 03.08.2026, QQS bilan</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>58850000</v>
+        <v>45934000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3869000</v>
+        <v>5295000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2391,392 +2396,397 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №161/26</t>
+          <t>Оплата за транспортные услуги по договору №24/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>54981000</v>
+        <v>40639000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>27387000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>10303000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №490 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №6151</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>82368000</v>
+        <v>30336000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>4061000</v>
+        <v>10239000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Termiz Metall MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №932</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №20/26, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>86429000</v>
+        <v>40575000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>4023000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>4085000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №122/26 от 04.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7813 за поставленный товар</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>82406000</v>
+        <v>44660000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>6458000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>915000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Shodlik Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>379893522</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000936368057001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №610</t>
+          <t>Оплата за овар по счет-фактуре №2694 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>75948000</v>
+        <v>45575000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>11294000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>971000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000626748669001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №2243 05.08.2026, QQS BILAN</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>87242000</v>
+        <v>44604000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>3778000</v>
+        <v>47393000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №291/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №2/26, НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>91020000</v>
+        <v>91997000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>4074000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>2892000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7552</t>
+          <t>Предоплата за товар по договору №245/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>86946000</v>
+        <v>94889000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>12608000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>2608000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата по счет-фактуре №8196 за поставленный товар</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>74338000</v>
+        <v>97497000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>29314000</v>
+        <v>2148000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Farovon Meva Eksport MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>301060917</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000162417270001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №4822 06.08.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №123/26, QQS 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>103652000</v>
+        <v>99645000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>9386000</v>
+        <v>3008000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2786,77 +2796,77 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №45/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №165/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>94266000</v>
+        <v>96637000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46241</v>
+        <v>46232</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>1698000</v>
+        <v>50890000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish Materiallari AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>295868307</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000737520516001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №35/23</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №9825</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>92568000</v>
+        <v>45747000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46244</v>
+        <v>46233</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>12793000</v>
+        <v>1022000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2866,37 +2876,37 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TOVAR UCUN TO'LOV, HISOB-FAKTURA №4313 10.08.2026, QQS BILAN</t>
+          <t>Оплата за товар по счет-фактуре №7549 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>105361000</v>
+        <v>46769000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46244</v>
+        <v>46233</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>6731000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>12485000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Bunyodkor Plastik MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>346876819</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000012955226001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,77 +2916,77 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8262 10.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №245/26</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>112092000</v>
+        <v>34284000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>5932000</v>
+        <v>716000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>339798935</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000299363680001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7879 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №2164 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>118024000</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>1907000</v>
+        <v>693000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2986,77 +2996,72 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №83/26 от 10.08.2026</t>
+          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>119931000</v>
+        <v>35693000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>1732000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>240347106</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №325</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>121663000</v>
+        <v>35393000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>7541000</v>
+        <v>2563000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3066,32 +3071,37 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №38/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №15/26, QQS bilan</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>114122000</v>
+        <v>32830000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>87052000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
+          <t>Termiz Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>16307000289377189417</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3101,37 +3111,37 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по дог. №214/26 от 04.08.2026</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>103622000</v>
+        <v>119882000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>3874000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>7580000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>241410824</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000645694245001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3141,237 +3151,232 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9810</t>
+          <t>Оплата за товар по с/ф №8459 от 04.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>99748000</v>
+        <v>127462000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>8869000</v>
+        <v>1641000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9943 от 04.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>108617000</v>
+        <v>129103000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>26969000</v>
+        <v>12608000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>293602204</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №139/26</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>81648000</v>
+        <v>116495000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>13533000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>1556000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9829</t>
+          <t>Предоплата за товар по дог. №73/26 от 05.08.2026</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>68115000</v>
+        <v>118051000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46248</v>
+        <v>46239</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>1944000</v>
+        <v>1360000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4972 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №68/26, НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>70059000</v>
+        <v>119411000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>10518000</v>
+        <v>1232000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №176/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №87/26, НДС 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>80577000</v>
+        <v>120643000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>4068000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>10433000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Bunyodkor Plastik MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>346876819</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000012955226001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,37 +3386,37 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №89/26 от 17.08.2026</t>
+          <t>Оплата за товары согласно с/ф №6282</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>84645000</v>
+        <v>110210000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>3706000</v>
+        <v>6557000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3421,117 +3426,117 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9970</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4899</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>88351000</v>
+        <v>116767000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>3101000</v>
+        <v>1671000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №66/26, QQS 12%</t>
+          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>91452000</v>
+        <v>118438000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>3048000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>3141000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №193/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №99/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>94500000</v>
+        <v>115297000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>2482000</v>
+        <v>2999000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3541,197 +3546,197 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №219/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №56/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>96982000</v>
+        <v>118296000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>1719000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>2791000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Оплата за товар по с/ф №5858 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>95263000</v>
+        <v>121087000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>1719000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>1018000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата за товар по с/ф №1855 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>93544000</v>
+        <v>122105000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>32378000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>11127000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №282/26</t>
+          <t>Оплата по счет-фактуре №4983 за поставленный товар</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>61166000</v>
+        <v>133232000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>56904000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>8406000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №176/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>4262000</v>
+        <v>141638000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>2360000</v>
+        <v>3251000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3741,37 +3746,37 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2124 18.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4914 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6622000</v>
+        <v>144889000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>7188000</v>
+        <v>2731000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3781,357 +3786,352 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>13810000</v>
+        <v>147620000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>2736000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>1286000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №53/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №227/26, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>11074000</v>
+        <v>148906000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>8281000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>1045000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>241410824</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000645694245001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №231/26</t>
+          <t>Оплата по счет-фактуре №5113 за поставленный товар</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2793000</v>
+        <v>149951000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>8926000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>1698000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>390795382</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000362230014001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6742 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №13/22</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>11719000</v>
+        <v>148253000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>4749000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>3574000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>252960573</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000584551622001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4549</t>
+          <t>Оплата за транспортные услуги по договору №156/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>16468000</v>
+        <v>144679000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>2497000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>392471364</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>16307000289377189417</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №36/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>18965000</v>
+        <v>134179000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>1475000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>3781000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5854 24.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №45/26</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>20440000</v>
+        <v>130398000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>2816000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>1149000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Оплата по с/ф №4958 за поставленный товар</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>17624000</v>
+        <v>131547000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>4837000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>4721000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4325</t>
+          <t>Оплата за товар по счет-фактуре №392 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>12787000</v>
+        <v>136268000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>7327000</v>
+        <v>2981000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4141,237 +4141,237 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9933 25.08.2026, QQS bilan</t>
+          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>20114000</v>
+        <v>139249000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>2802000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>64350000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6280 25.08.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №129/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>22916000</v>
+        <v>74899000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>1061000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>2358000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000783144546001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6598 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>21855000</v>
+        <v>77257000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46260</v>
+        <v>46248</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>7546000</v>
+        <v>2061000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2789 26.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №256/26 от 14.08.2026</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>29401000</v>
+        <v>79318000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46260</v>
+        <v>46248</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>4659000</v>
+        <v>1719000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8617</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>24742000</v>
+        <v>77599000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46261</v>
+        <v>46248</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>2000000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>1719000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7534 27.08.2026, QQS bilan</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>26742000</v>
+        <v>75880000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>1468000</v>
+        <v>12090000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4381,352 +4381,357 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №248/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>28210000</v>
+        <v>87970000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46262</v>
+        <v>46251</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>7101000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>6917000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №179/26, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №196/26, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>21109000</v>
+        <v>94887000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>5516000</v>
+        <v>5654000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8850 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>26625000</v>
+        <v>100541000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>3151000</v>
+        <v>3679000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Shodlik Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>379893522</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000936368057001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8232</t>
+          <t>Оплата за продукцию по договору №79/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>29776000</v>
+        <v>104220000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>3014000</v>
+        <v>1858000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Shodlik Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>379893522</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000936368057001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9777 31.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №251/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>32790000</v>
+        <v>106078000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>2321000</v>
+        <v>1150000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>339798935</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000299363680001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6258 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №668 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>35111000</v>
+        <v>107228000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>1594000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>5617000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SHARTNOMA №207/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за материалы по дог. №224/26</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>36705000</v>
+        <v>101611000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>5945000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата по счет-фактуре №5749 за поставленный товар</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>36405000</v>
+        <v>107556000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>2487000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>2354000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №133/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4165</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>33918000</v>
+        <v>109910000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>3107000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>2106000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4736,37 +4741,37 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7989</t>
+          <t>Оплата за продукцию по договору №161/26, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>30811000</v>
+        <v>112016000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46266</v>
+        <v>46252</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>3942000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>3828000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4776,77 +4781,77 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9831</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>34753000</v>
+        <v>108188000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46267</v>
+        <v>46253</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>5377000</v>
+        <v>4126000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5242</t>
+          <t>Оплата за товар по счет-фактуре №7384 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>40130000</v>
+        <v>112314000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46267</v>
+        <v>46253</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1874000</v>
+        <v>1820000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4856,37 +4861,37 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №281/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7620 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>42004000</v>
+        <v>114134000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>85255000</v>
+        <v>3747000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4896,117 +4901,117 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №205/26</t>
+          <t>Оплата за товары согласно счет-фактуре №1357</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>-43251000</v>
+        <v>110387000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>44729000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Mehnat Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>339798935</t>
+          <t>252960573</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000299363680001</t>
+          <t>20208000584551622001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №45/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №215/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1478000</v>
+        <v>105127000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46269</v>
+        <v>46255</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>6560000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>57709000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №77/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5536</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>8038000</v>
+        <v>47418000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>1754000</v>
+        <v>1485000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5016,37 +5021,37 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №175/2, QQS 12%</t>
+          <t>Shartnoma №99/26 o'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>9792000</v>
+        <v>48903000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>24578000</v>
+        <v>1068000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5056,157 +5061,157 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5831 07.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №9476 24.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>34370000</v>
+        <v>49971000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>13134000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>1061000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000626748669001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №9/26, QQS 12%</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>47504000</v>
+        <v>48910000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>5356000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>2548000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №256/26 bo'yicha oldinan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №5437</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>52860000</v>
+        <v>46362000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>4995000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>2815000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №176/26, НДС 12%</t>
+          <t>НДС ЗА ИЮЛЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>57855000</v>
+        <v>43547000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>4377000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>3784000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Farg'ona Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>241082476</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000569424555001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5216,77 +5221,77 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5480 07.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №7215</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>62232000</v>
+        <v>39763000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>1975000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>6311000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №46/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №67/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>64207000</v>
+        <v>33452000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>1164000</v>
+        <v>4023000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5296,117 +5301,117 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4256 07.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1112 ОТ 25.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>65371000</v>
+        <v>37475000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>1005000</v>
+        <v>3804000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
+          <t>Tovar uchun to'lv, hisob-faktura №5087 25.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>66376000</v>
+        <v>41279000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>1724000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>9116000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №223/26 от 07.09.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7881 26.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>64652000</v>
+        <v>50395000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>2193000</v>
+        <v>3777000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo MChJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>241410824</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000645694245001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5416,37 +5421,37 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №14/26</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6825</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>62459000</v>
+        <v>46618000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>5056000</v>
+        <v>11886000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5456,32 +5461,37 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №223/26</t>
+          <t>Оплата за товары согласно счет-фактуре №9917</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>57403000</v>
+        <v>34732000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>13292000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>1063000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Termiz Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5491,117 +5501,117 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №7066</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9203</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>44111000</v>
+        <v>35795000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>4744000</v>
+        <v>6777000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2434 от 08.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №89/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>48855000</v>
+        <v>42572000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>2970000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>1540000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №50/26 от 08.09.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №49/26, QQS 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>45885000</v>
+        <v>44112000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>3196000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>1394000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5611,237 +5621,232 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №270/26 от 08.09.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8845 за поставленный товар</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>42689000</v>
+        <v>45506000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>2991000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>370885713</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за подукцию по договору №97/26, НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>45680000</v>
+        <v>45206000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>2321000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>3724000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>252960573</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000584551622001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №259/26 ОТ 09.09.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №55/26</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>48001000</v>
+        <v>41482000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>1790000</v>
+        <v>8189000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish Materiallari AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>295868307</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000737520516001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №35/23</t>
+          <t>Оплата за товары согласно счет-фактуре №8876</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46211000</v>
+        <v>33293000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>4605000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>4800000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №99/26</t>
+          <t>Оплата за товар по с/ф №5689 от 01.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>41606000</v>
+        <v>38093000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>30509000</v>
+        <v>13071000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Samarqand Meva Eksport MChJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>362946385</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000761903215001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7369</t>
+          <t>Оплата за сырье по дог. №251/26 от 01.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>11097000</v>
+        <v>25022000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>3060000</v>
+        <v>2896000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5851,432 +5856,432 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>14157000</v>
+        <v>27918000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>17280000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>16307000289377189417</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №9401 за поставленный товар</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>3657000</v>
+        <v>45198000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>7022000</v>
+        <v>7414000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1230 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>10679000</v>
+        <v>52612000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>2115000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>13292000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>392471364</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №726 14.09.2026, QQS bilan</t>
+          <t>Avgust oyi uchun ish haqi, reestr №5775</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>12794000</v>
+        <v>39320000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>1519000</v>
+        <v>21335000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6161 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №7108 за поставленный товар</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>14313000</v>
+        <v>60655000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>1162000</v>
+        <v>11038000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №289/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №14/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>15475000</v>
+        <v>71693000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>1812000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>7496000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №87/26, НДС 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>13663000</v>
+        <v>79189000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1812000</v>
+        <v>1790000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390795382</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000362230014001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>НДФЛ ЗА АВГУСТ 2026</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №13/22</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>11851000</v>
+        <v>77399000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>3500000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>3431000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7346 15.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №223/26</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>15351000</v>
+        <v>73968000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>3413000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №223/26, QQS bilan</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>18764000</v>
+        <v>54128000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>1475000</v>
+        <v>23640000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Termiz Metall MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №8089 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>20239000</v>
+        <v>77768000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>4064000</v>
+        <v>6323000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,37 +6291,37 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №580</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1204 ОТ 08.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>24303000</v>
+        <v>84091000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>2280000</v>
+        <v>4889000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6326,37 +6331,37 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №41/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №719 08.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>26583000</v>
+        <v>88980000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>1687000</v>
+        <v>3697000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,37 +6371,37 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Shartnoma №297/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5986 08.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>28270000</v>
+        <v>92677000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>1584000</v>
+        <v>7202000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6406,197 +6411,192 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2849</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7926</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>29854000</v>
+        <v>99879000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1603000</v>
+        <v>7677000</v>
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №204/26</t>
+          <t>Оплата за транспортные услуги по дог. №53/26</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>28251000</v>
+        <v>92202000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>2097000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>370885713</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2904)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>16307000289377189417</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №156/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-2904 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>30348000</v>
+        <v>81702000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>2051000</v>
-      </c>
+      <c r="C158" s="2" t="n">
+        <v>4605000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №126/26 от 18.09.2026</t>
+          <t>Оплата за транспортные услуги по договору №263/26</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>32399000</v>
+        <v>77097000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>50468000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>19775000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №50/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №5212 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>-18069000</v>
+        <v>96872000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>39112000</v>
+        <v>4656000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6606,37 +6606,37 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2348 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>21043000</v>
+        <v>101528000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>3355000</v>
+        <v>4020000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6646,277 +6646,277 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №84/26, НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>24398000</v>
+        <v>105548000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>2224000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>9950000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Angren Qurilish XK</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>309305032</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000414067636001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6406 21.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7703</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>26622000</v>
+        <v>95598000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>1706000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>4822000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2648</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1262</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>24916000</v>
+        <v>100420000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>2368000</v>
+        <v>1812000</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2654</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>22548000</v>
+        <v>98608000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>5739000</v>
+        <v>1812000</v>
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №198/26</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>16809000</v>
+        <v>96796000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>2969000</v>
+        <v>11955000</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Tovarlar uchun to'lov h/f №9395</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>13840000</v>
+        <v>84841000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>2207000</v>
+        <v>63758000</v>
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Avto Ehtiyot MChJ</t>
+          <t>Farovon Plastik AJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>394529605</t>
+          <t>272048821</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000305845516001</t>
+          <t>20208000556791956001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №180/26</t>
+          <t>Оплата за сырье по договору №50/26 от 18.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>11633000</v>
+        <v>21083000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>3581000</v>
+        <v>18118000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6926,77 +6926,77 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №833 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №144/6, QQS 12%</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>15214000</v>
+        <v>39201000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>1611000</v>
+        <v>9386000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №31 24.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №37/26, НДС 12%</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>16825000</v>
+        <v>48587000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="n">
-        <v>1127000</v>
+        <v>7858000</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7006,37 +7006,37 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договор №54/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №38/26, НДС 12%</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>17952000</v>
+        <v>56445000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B171" t="n">
         <v>263</v>
       </c>
       <c r="C171" s="2" t="n"/>
       <c r="D171" s="2" t="n">
-        <v>1355000</v>
+        <v>5436000</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Denov Tur Servis MChJ</t>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>370885713</t>
+          <t>247136433</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000784957864001</t>
+          <t>20208000449972399001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7046,391 +7046,631 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №201/26 от 25.09.2026</t>
+          <t>Оплата за продукцию по договору №22/26, НДС 12%</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>19307000</v>
+        <v>61881000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>1833000</v>
+        <v>2931000</v>
       </c>
       <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Samarqand Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>362946385</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000761903215001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №35/26</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>17474000</v>
+        <v>58950000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>3253000</v>
+        <v>3464000</v>
       </c>
       <c r="D173" s="2" t="n"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Chust Sut AJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>260220479</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000785766169001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4593</t>
+          <t>Предоплата за материалы по договору №153/26</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>14221000</v>
+        <v>55486000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B174" t="n">
         <v>266</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>3974000</v>
+        <v>9636000</v>
       </c>
       <c r="D174" s="2" t="n"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Omad Yog' Zavodi MChJ</t>
+          <t>Mehnat Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>293720488</t>
+          <t>252960573</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000115567919001</t>
+          <t>20208000584551622001</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №74/26</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>10247000</v>
+        <v>45850000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B175" t="n">
         <v>267</v>
       </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>10108000</v>
-      </c>
+      <c r="C175" s="2" t="n">
+        <v>4663000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Jizzax Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>234710679</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000321420513001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1525 28.09.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5527</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>20355000</v>
+        <v>41187000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B176" t="n">
         <v>268</v>
       </c>
-      <c r="C176" s="2" t="n">
-        <v>1118000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>6814000</v>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>288571337</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20208000783144546001</t>
+          <t>20208000495786439001</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
+          <t>Предоплата за товар по договору №180/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>19237000</v>
+        <v>48001000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B177" t="n">
         <v>269</v>
       </c>
-      <c r="C177" s="2" t="n">
-        <v>5554000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>5148000</v>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Oqtosh Non AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>293602204</t>
+          <t>206091701</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20208000957857661001</t>
+          <t>20208000241727087001</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №279/26</t>
+          <t>Предоплата за товар по договору №255/26 от 25.09.2026</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>13683000</v>
+        <v>53149000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="B178" t="n">
         <v>270</v>
       </c>
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="n">
-        <v>16095000</v>
+        <v>2840000</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och AJ</t>
+          <t>Termiz Metall MChJ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>392471364</t>
+          <t>330503264</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>20208000344499723001</t>
+          <t>20208000406763636001</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hf №4810 29.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2250</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>29778000</v>
+        <v>55989000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B179" t="n">
         <v>271</v>
       </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>922000</v>
-      </c>
+      <c r="C179" s="2" t="n">
+        <v>37995000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Farovon Plastik AJ</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>240347106</t>
+          <t>272048821</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>20208000963214205001</t>
+          <t>20208000556791956001</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4717 30.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №72/26</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>30700000</v>
+        <v>17994000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B180" t="n">
         <v>272</v>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>31208000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Shodlik Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>379893522</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000936368057001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Shartnoma №62/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>49202000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>3124000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>247136433</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000449972399001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №279/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>52326000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B182" t="n">
+        <v>274</v>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>3075000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Kattaqo'rg'on Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>247136433</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000449972399001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №225/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>55401000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B183" t="n">
+        <v>275</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>1118000</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000626748669001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнегию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>54283000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B184" t="n">
+        <v>276</v>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>18628000</v>
+      </c>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Jizzax Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>234710679</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000321420513001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по дог. №235/26</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>35655000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B185" t="n">
+        <v>277</v>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>4955000</v>
+      </c>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Jizzax Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>234710679</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20208000321420513001</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Предоплата а материалы по договору №258/26</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>30700000</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B186" t="n">
+        <v>278</v>
+      </c>
+      <c r="C186" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" t="inlineStr">
         <is>
           <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>01153</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
         <v>30400000</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C181" s="4" t="n">
-        <v>696244000</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>695244000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="C187" s="4" t="n">
+        <v>694579000</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>693579000</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C182" s="4" t="n">
+      <c r="C188" s="4" t="n">
         <v>30400000</v>
       </c>
-      <c r="D182" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
